--- a/Test Results/Excel/Passed_Test_Cases.xlsx
+++ b/Test Results/Excel/Passed_Test_Cases.xlsx
@@ -52516,7 +52516,7 @@
         </is>
       </c>
       <c r="G1487" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1488">
@@ -52551,7 +52551,7 @@
         </is>
       </c>
       <c r="G1488" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1489">
@@ -52586,7 +52586,7 @@
         </is>
       </c>
       <c r="G1489" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1490">
@@ -52621,7 +52621,7 @@
         </is>
       </c>
       <c r="G1490" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1491">
@@ -52656,7 +52656,7 @@
         </is>
       </c>
       <c r="G1491" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1492">
@@ -52691,7 +52691,7 @@
         </is>
       </c>
       <c r="G1492" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1493">
@@ -52726,7 +52726,7 @@
         </is>
       </c>
       <c r="G1493" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1494">
@@ -52761,7 +52761,7 @@
         </is>
       </c>
       <c r="G1494" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1495">
@@ -52796,7 +52796,7 @@
         </is>
       </c>
       <c r="G1495" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1496">
@@ -52831,7 +52831,7 @@
         </is>
       </c>
       <c r="G1496" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1497">
@@ -52866,7 +52866,7 @@
         </is>
       </c>
       <c r="G1497" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1498">
@@ -52901,7 +52901,7 @@
         </is>
       </c>
       <c r="G1498" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1499">
@@ -52936,7 +52936,7 @@
         </is>
       </c>
       <c r="G1499" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1500">
@@ -52971,7 +52971,7 @@
         </is>
       </c>
       <c r="G1500" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1501">
@@ -53006,7 +53006,7 @@
         </is>
       </c>
       <c r="G1501" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1502">
@@ -53041,7 +53041,7 @@
         </is>
       </c>
       <c r="G1502" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1503">
@@ -53076,7 +53076,7 @@
         </is>
       </c>
       <c r="G1503" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1504">
@@ -53111,7 +53111,7 @@
         </is>
       </c>
       <c r="G1504" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1505">
@@ -53146,7 +53146,7 @@
         </is>
       </c>
       <c r="G1505" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1506">
@@ -53181,7 +53181,7 @@
         </is>
       </c>
       <c r="G1506" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1507">
@@ -53216,7 +53216,7 @@
         </is>
       </c>
       <c r="G1507" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1508">
@@ -53251,7 +53251,7 @@
         </is>
       </c>
       <c r="G1508" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1509">
@@ -53286,7 +53286,7 @@
         </is>
       </c>
       <c r="G1509" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1510">
@@ -53321,7 +53321,7 @@
         </is>
       </c>
       <c r="G1510" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1511">
@@ -53356,7 +53356,7 @@
         </is>
       </c>
       <c r="G1511" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1512">
@@ -53391,7 +53391,7 @@
         </is>
       </c>
       <c r="G1512" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1513">
@@ -53426,7 +53426,7 @@
         </is>
       </c>
       <c r="G1513" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1514">
@@ -53461,7 +53461,7 @@
         </is>
       </c>
       <c r="G1514" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1515">
@@ -53496,7 +53496,7 @@
         </is>
       </c>
       <c r="G1515" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1516">
@@ -53531,7 +53531,7 @@
         </is>
       </c>
       <c r="G1516" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1517">
@@ -53566,7 +53566,7 @@
         </is>
       </c>
       <c r="G1517" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1518">
@@ -53601,7 +53601,7 @@
         </is>
       </c>
       <c r="G1518" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1519">
@@ -53636,7 +53636,7 @@
         </is>
       </c>
       <c r="G1519" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1520">
@@ -53671,7 +53671,7 @@
         </is>
       </c>
       <c r="G1520" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1521">
@@ -53706,7 +53706,7 @@
         </is>
       </c>
       <c r="G1521" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
